--- a/public/templates/office/EMP_FIN_010_월간_AI_FinOps_토큰정산보고서.xlsx
+++ b/public/templates/office/EMP_FIN_010_월간_AI_FinOps_토큰정산보고서.xlsx
@@ -65,7 +65,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001E293B"/>
+        <fgColor rgb="000F2942"/>
       </patternFill>
     </fill>
   </fills>
@@ -473,7 +473,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="72" customWidth="1" min="3" max="3"/>
+    <col width="78" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="2">
@@ -491,7 +491,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>한빛글로벌 엔터프라이즈 AI 콘텐츠·규제 심의 자동화 시스템(SyncGuard AI) 구축 및 운영</t>
+          <t>한빛글로벌 지능형 공급망 구매·조달 계약 및 부품 품질규격 AI 검증 플랫폼(SyncFlow AI) 구축 및 운영</t>
         </is>
       </c>
     </row>
@@ -617,22 +617,22 @@
   <dimension ref="B2:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>1. LLM / 비전 OCR / 임베딩 모델별 월간 토큰 사용량 및 정산 명세</t>
+          <t>1. LLM / 도면·문서 OCR / 임베딩 모델별 월간 토큰 사용량 및 정산 명세</t>
         </is>
       </c>
     </row>
@@ -696,12 +696,12 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>문서/시안 텍스트 추출</t>
+          <t>계약서·기술시방서 텍스트 파싱</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Clova OCR / PaddleOCR Hybrid</t>
+          <t>Enterprise Vision OCR Engine</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>고해상도 상세페이지</t>
+          <t>다단 계약서·스캔 시방서</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>동영상 키프레임 비전 분석</t>
+          <t>CAD 설계도면 규격표 비전 분석</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>피크프레임 추출 후 호출</t>
+          <t>도면 표제란·공차 추출</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>1차 경량 규칙·유형 분류</t>
+          <t>1차 경량 독소조항·BOM 규격 분류</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>저위험 문장 즉시 필터링</t>
+          <t>저위험 조항 즉시 필터링</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>2차 정밀 규제 심의·대체문안</t>
+          <t>2차 정밀 하도급법·표준 수정조항 생성</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>고위험·복합 문맥 추론</t>
+          <t>고위험 독소조항 Redline 추론</t>
         </is>
       </c>
     </row>
@@ -1014,20 +1014,20 @@
   <dimension ref="B2:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>2. 사업부 / 브랜드별 AI 토큰 비용 차지백(Chargeback) 배부표</t>
+          <t>2. 사업본부별 AI 토큰 비용 차지백(Chargeback) 배부표</t>
         </is>
       </c>
     </row>
@@ -1039,17 +1039,17 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>사업부 / 부서명</t>
+          <t>사업본부명</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>대상 브랜드</t>
+          <t>주요 검증 품목군</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>월간 심의 의뢰(건)</t>
+          <t>월간 검증 건수(건)</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
@@ -1081,12 +1081,12 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>럭셔리뷰티사업부</t>
+          <t>전장시스템본부</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>루미에르 (Lumiere)</t>
+          <t>구동모터 제어기(MCU) · 인포테인먼트</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>프리미엄스킨케어부</t>
+          <t>정밀기계본부</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>벨르코어 (BelleCore)</t>
+          <t>전동 조향 기어박스(EPS) · 제동모듈</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>더마코스메틱사업부</t>
+          <t>스마트팩토리본부</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>더마쉴드 (DermaShield)</t>
+          <t>자율주행 물류로봇(AMR) · 비전센서</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>디지털마케팅실</t>
+          <t>배터리모듈·글로벌조달본부</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>아쿠아퓨어 / 그린네이처</t>
+          <t>고전압 버스바 · 북미/유럽 수출계약</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
